--- a/datos/directorio_casas_juventud.xlsx
+++ b/datos/directorio_casas_juventud.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carol\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carol\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE5A21E-42C3-4192-88DC-D8D96C5EE3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6652348-2101-4BF8-9FC6-0B00DF07860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
   <si>
     <t>Casa de Juventud</t>
   </si>
@@ -251,6 +251,66 @@
   </si>
   <si>
     <t>Barrancas</t>
+  </si>
+  <si>
+    <t>Link Google Maps</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oVjNxRHJpE97bkJt7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Qx952p9uusAus2Fe9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/iDiSK3FDATFemp2w9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xRmvfH9gkVxYtJg49</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4fRNhTZD9vWbjggF9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dncs1kGJK9riiyYS6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QJFQccMcPHBphmocA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/v3PGh3Uo2wETr3847</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cSscBzPP9THgun7L9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kpe1jz5LnjrPJezj6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vfmZKVfAttCJV6w29</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5bL3m7G2EFxHdMK99</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Ar3upbJtnuc253dM7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Sr3TPbJcnM9BqfT98</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/yJApYtmgjPxYfzAF6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/MvaKotdmWKKvNHCY8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/82UyQF2ZdhqxkKmr9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cushqfp7wQp3QaGE9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8iweeWHjrcWsdKND7</t>
   </si>
 </sst>
 </file>
@@ -258,9 +318,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.0000000000000"/>
+    <numFmt numFmtId="164" formatCode="0.0000000000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +332,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -321,20 +389,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -646,6 +718,7 @@
     <col min="4" max="4" width="16.46484375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="31.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -668,6 +741,9 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
@@ -688,6 +764,9 @@
       <c r="F2" s="7">
         <v>-74.103246468893303</v>
       </c>
+      <c r="G2" s="8" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
@@ -708,6 +787,9 @@
       <c r="F3" s="7">
         <v>-74.077943787523495</v>
       </c>
+      <c r="G3" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
@@ -729,6 +811,9 @@
       <c r="F4" s="7">
         <v>-74.193902501018101</v>
       </c>
+      <c r="G4" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
@@ -749,6 +834,9 @@
       <c r="F5" s="7">
         <v>-74.069944935161502</v>
       </c>
+      <c r="G5" s="8" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
@@ -769,6 +857,9 @@
       <c r="F6" s="7">
         <v>-74.054178481485096</v>
       </c>
+      <c r="G6" s="8" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
@@ -789,6 +880,9 @@
       <c r="F7" s="7">
         <v>-74.139195919818505</v>
       </c>
+      <c r="G7" s="8" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
@@ -809,6 +903,9 @@
       <c r="F8" s="7">
         <v>-74.162166277490002</v>
       </c>
+      <c r="G8" s="8" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
@@ -829,6 +926,9 @@
       <c r="F9" s="7">
         <v>-74.109543717967796</v>
       </c>
+      <c r="G9" s="8" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
@@ -849,6 +949,9 @@
       <c r="F10" s="7">
         <v>-74.156304182385796</v>
       </c>
+      <c r="G10" s="8" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
@@ -869,6 +972,9 @@
       <c r="F11" s="5">
         <v>-74.156251390982604</v>
       </c>
+      <c r="G11" s="9" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
@@ -889,6 +995,9 @@
       <c r="F12" s="5">
         <v>-74.081139060296394</v>
       </c>
+      <c r="G12" s="9" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
@@ -909,6 +1018,9 @@
       <c r="F13" s="5">
         <v>-74.109366760296595</v>
       </c>
+      <c r="G13" s="9" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
@@ -929,6 +1041,9 @@
       <c r="F14" s="5">
         <v>-74.0824997875267</v>
       </c>
+      <c r="G14" s="9" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
@@ -949,6 +1064,9 @@
       <c r="F15" s="5">
         <v>-74.108112775639199</v>
       </c>
+      <c r="G15" s="9" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
@@ -969,8 +1087,11 @@
       <c r="F16" s="5">
         <v>-74.114615635161499</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G16" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
@@ -989,8 +1110,11 @@
       <c r="F17" s="5">
         <v>-74.105577204475395</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G17" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -1009,8 +1133,11 @@
       <c r="F18" s="5">
         <v>-74.166916680596202</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G18" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
@@ -1029,8 +1156,11 @@
       <c r="F19" s="5">
         <v>-74.103284019818503</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G19" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>24</v>
       </c>
@@ -1049,8 +1179,32 @@
       <c r="F20" s="5">
         <v>-74.025570338939303</v>
       </c>
+      <c r="G20" s="9" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{83F22C8F-ABDF-493B-B13E-16498F100558}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{7BCF2274-412C-4498-9359-E6CE0CDF6C89}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{DD5AEA9B-A749-4818-B108-8D9029B9FC03}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{866C1BBD-C919-4F70-9BD8-DC542D84B2E5}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{D0698ACF-4894-4389-8288-456536426462}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{FAD91E18-75AC-4AD7-904A-FE51A23F653F}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{8C4F983F-C0E7-4791-B54D-C65DFD8D1DFF}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{6A33BACC-D86F-4A53-8554-D2CF64DB9EE8}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{DDE3DE27-5CD6-4991-8F52-BF8E1D25C31F}"/>
+    <hyperlink ref="G12" r:id="rId10" xr:uid="{CEBF6445-BFD5-4BD1-ACA8-A087A2C4528C}"/>
+    <hyperlink ref="G11" r:id="rId11" xr:uid="{93E9159C-7749-4665-9DEF-E477AD18900C}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{D6323970-9B33-4090-96F4-3F78EB9866F5}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{5DA4A7F0-C367-40B1-8D7E-5E0B0CF7DD0F}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{4E9640AF-BAE2-4117-8B6A-1ED40DB47EC1}"/>
+    <hyperlink ref="G16" r:id="rId15" xr:uid="{895EE8B2-5E34-4E74-A5A5-065F5F0ACD07}"/>
+    <hyperlink ref="G17" r:id="rId16" xr:uid="{F17E10DF-492A-4ACE-A982-7E4706946D81}"/>
+    <hyperlink ref="G18" r:id="rId17" xr:uid="{940EDECE-B748-4F8A-8491-8D840CD3B75D}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{B574D969-8955-4DD7-8DED-715F201DCE52}"/>
+    <hyperlink ref="G20" r:id="rId19" xr:uid="{5FC19BD3-217D-40E0-9D62-51866404657B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos/directorio_casas_juventud.xlsx
+++ b/datos/directorio_casas_juventud.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carol\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\datos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6652348-2101-4BF8-9FC6-0B00DF07860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
   <si>
     <t>Casa de Juventud</t>
   </si>
@@ -40,6 +34,12 @@
     <t>Longitud</t>
   </si>
   <si>
+    <t>Correo</t>
+  </si>
+  <si>
+    <t>Link Google Maps</t>
+  </si>
+  <si>
     <t>Antonio Nariño</t>
   </si>
   <si>
@@ -139,7 +139,7 @@
     <t>Tunjuelito</t>
   </si>
   <si>
-    <t>Cra. 22 # 19-26 Sur</t>
+    <t>Cra. 20 # 19 Sur - 26</t>
   </si>
   <si>
     <t>Calle 73 # 51 - 27</t>
@@ -187,7 +187,7 @@
     <t>Cra. 32a #1h-06</t>
   </si>
   <si>
-    <t>Diagonal 73C #57-17</t>
+    <t>Dg. 73 C # 57 - 17 Sur</t>
   </si>
   <si>
     <t>Diagonal 47 Sur #53 - 41</t>
@@ -253,7 +253,61 @@
     <t>Barrancas</t>
   </si>
   <si>
-    <t>Link Google Maps</t>
+    <t>cdj-antonionarino@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-nasqua@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-josesaramago@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-nachosanchez@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-chapinero@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-ayelen@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-paraiso@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-aldeadepensadores@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-huitaca@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-iwoka@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-cacma@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-rafaeluribeuribe@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-damawha@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-diegofelipebecerra@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-frailejon@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-puentearanda@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-ecoparque@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-tunjuelito@sdis.gov.co</t>
+  </si>
+  <si>
+    <t>cdj-usaquen@sdis.gov.co</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/oVjNxRHJpE97bkJt7</t>
@@ -316,11 +370,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000000000000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,27 +393,14 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -375,57 +413,47 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -463,7 +491,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -497,7 +525,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -532,10 +559,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -708,21 +734,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="34.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.46484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.73046875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,468 +758,527 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2">
+        <v>4.58515770741139</v>
+      </c>
+      <c r="F2">
+        <v>-74.1032464688933</v>
+      </c>
+      <c r="G2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3">
+        <v>4.6689440006099</v>
+      </c>
+      <c r="F3">
+        <v>-74.07794378752349</v>
+      </c>
+      <c r="G3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4">
+        <v>4.61273867108817</v>
+      </c>
+      <c r="F4">
+        <v>-74.1939025010181</v>
+      </c>
+      <c r="G4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5">
+        <v>4.59287910555281</v>
+      </c>
+      <c r="F5">
+        <v>-74.0699449351615</v>
+      </c>
+      <c r="G5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>4.64669635000169</v>
+      </c>
+      <c r="F6">
+        <v>-74.0541784814851</v>
+      </c>
+      <c r="G6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7">
+        <v>4.55290308504347</v>
+      </c>
+      <c r="F7">
+        <v>-74.1391959198185</v>
+      </c>
+      <c r="G7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8">
+        <v>4.55137692050011</v>
+      </c>
+      <c r="F8">
+        <v>-74.16216627749</v>
+      </c>
+      <c r="G8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9">
+        <v>4.69471990918243</v>
+      </c>
+      <c r="F9">
+        <v>-74.1095437179678</v>
+      </c>
+      <c r="G9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10">
+        <v>4.68501707869691</v>
+      </c>
+      <c r="F10">
+        <v>-74.1563041823858</v>
+      </c>
+      <c r="G10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11">
+        <v>4.62365097381033</v>
+      </c>
+      <c r="F11">
+        <v>-74.1562513909826</v>
+      </c>
+      <c r="G11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12">
+        <v>4.62273316196456</v>
+      </c>
+      <c r="F12">
+        <v>-74.08113906029639</v>
+      </c>
+      <c r="G12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13">
+        <v>4.55152167051123</v>
+      </c>
+      <c r="F13">
+        <v>-74.1093667602966</v>
+      </c>
+      <c r="G13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14">
+        <v>4.57624535479972</v>
+      </c>
+      <c r="F14">
+        <v>-74.0824997875267</v>
+      </c>
+      <c r="G14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15">
+        <v>4.74117558266255</v>
+      </c>
+      <c r="F15">
+        <v>-74.1081127756392</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16">
+        <v>4.51240857618561</v>
+      </c>
+      <c r="F16">
+        <v>-74.1146156351615</v>
+      </c>
+      <c r="G16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17">
+        <v>4.60368500294662</v>
+      </c>
+      <c r="F17">
+        <v>-74.1055772044754</v>
+      </c>
+      <c r="G17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18">
+        <v>4.57712207018447</v>
+      </c>
+      <c r="F18">
+        <v>-74.1669166805962</v>
+      </c>
+      <c r="G18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="7">
-        <v>4.5851577074113896</v>
-      </c>
-      <c r="F2" s="7">
-        <v>-74.103246468893303</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="E19">
+        <v>4.58522187440551</v>
+      </c>
+      <c r="F19">
+        <v>-74.1032840198185</v>
+      </c>
+      <c r="G19" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="7">
-        <v>4.6689440006099003</v>
-      </c>
-      <c r="F3" s="7">
-        <v>-74.077943787523495</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="7">
-        <v>4.6127386710881702</v>
-      </c>
-      <c r="F4" s="7">
-        <v>-74.193902501018101</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="7">
-        <v>4.59287910555281</v>
-      </c>
-      <c r="F5" s="7">
-        <v>-74.069944935161502</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="7">
-        <v>4.6466963500016902</v>
-      </c>
-      <c r="F6" s="7">
-        <v>-74.054178481485096</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="7">
-        <v>4.5529030850434697</v>
-      </c>
-      <c r="F7" s="7">
-        <v>-74.139195919818505</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="7">
-        <v>4.5513769205001102</v>
-      </c>
-      <c r="F8" s="7">
-        <v>-74.162166277490002</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="7">
-        <v>4.6947199091824299</v>
-      </c>
-      <c r="F9" s="7">
-        <v>-74.109543717967796</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="7">
-        <v>4.6850170786969096</v>
-      </c>
-      <c r="F10" s="7">
-        <v>-74.156304182385796</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="5">
-        <v>4.6236509738103297</v>
-      </c>
-      <c r="F11" s="5">
-        <v>-74.156251390982604</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="5">
-        <v>4.6227331619645602</v>
-      </c>
-      <c r="F12" s="5">
-        <v>-74.081139060296394</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="5">
-        <v>4.5515216705112298</v>
-      </c>
-      <c r="F13" s="5">
-        <v>-74.109366760296595</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="5">
-        <v>4.5762453547997204</v>
-      </c>
-      <c r="F14" s="5">
-        <v>-74.0824997875267</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="5">
-        <v>4.7411755826625503</v>
-      </c>
-      <c r="F15" s="5">
-        <v>-74.108112775639199</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="5">
-        <v>4.5124085761856101</v>
-      </c>
-      <c r="F16" s="5">
-        <v>-74.114615635161499</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="5">
-        <v>4.6036850029466203</v>
-      </c>
-      <c r="F17" s="5">
-        <v>-74.105577204475395</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="5">
-        <v>4.5771220701844699</v>
-      </c>
-      <c r="F18" s="5">
-        <v>-74.166916680596202</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="5">
-        <v>4.5852218744055104</v>
-      </c>
-      <c r="F19" s="5">
-        <v>-74.103284019818503</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="5">
-        <v>4.7342311274868196</v>
-      </c>
-      <c r="F20" s="5">
-        <v>-74.025570338939303</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>96</v>
+      <c r="E20">
+        <v>4.73423112748682</v>
+      </c>
+      <c r="F20">
+        <v>-74.0255703389393</v>
+      </c>
+      <c r="G20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{83F22C8F-ABDF-493B-B13E-16498F100558}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{7BCF2274-412C-4498-9359-E6CE0CDF6C89}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{DD5AEA9B-A749-4818-B108-8D9029B9FC03}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{866C1BBD-C919-4F70-9BD8-DC542D84B2E5}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{D0698ACF-4894-4389-8288-456536426462}"/>
-    <hyperlink ref="G7" r:id="rId6" xr:uid="{FAD91E18-75AC-4AD7-904A-FE51A23F653F}"/>
-    <hyperlink ref="G8" r:id="rId7" xr:uid="{8C4F983F-C0E7-4791-B54D-C65DFD8D1DFF}"/>
-    <hyperlink ref="G9" r:id="rId8" xr:uid="{6A33BACC-D86F-4A53-8554-D2CF64DB9EE8}"/>
-    <hyperlink ref="G10" r:id="rId9" xr:uid="{DDE3DE27-5CD6-4991-8F52-BF8E1D25C31F}"/>
-    <hyperlink ref="G12" r:id="rId10" xr:uid="{CEBF6445-BFD5-4BD1-ACA8-A087A2C4528C}"/>
-    <hyperlink ref="G11" r:id="rId11" xr:uid="{93E9159C-7749-4665-9DEF-E477AD18900C}"/>
-    <hyperlink ref="G13" r:id="rId12" xr:uid="{D6323970-9B33-4090-96F4-3F78EB9866F5}"/>
-    <hyperlink ref="G14" r:id="rId13" xr:uid="{5DA4A7F0-C367-40B1-8D7E-5E0B0CF7DD0F}"/>
-    <hyperlink ref="G15" r:id="rId14" xr:uid="{4E9640AF-BAE2-4117-8B6A-1ED40DB47EC1}"/>
-    <hyperlink ref="G16" r:id="rId15" xr:uid="{895EE8B2-5E34-4E74-A5A5-065F5F0ACD07}"/>
-    <hyperlink ref="G17" r:id="rId16" xr:uid="{F17E10DF-492A-4ACE-A982-7E4706946D81}"/>
-    <hyperlink ref="G18" r:id="rId17" xr:uid="{940EDECE-B748-4F8A-8491-8D840CD3B75D}"/>
-    <hyperlink ref="G19" r:id="rId18" xr:uid="{B574D969-8955-4DD7-8DED-715F201DCE52}"/>
-    <hyperlink ref="G20" r:id="rId19" xr:uid="{5FC19BD3-217D-40E0-9D62-51866404657B}"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
